--- a/data/trans_dic/IP12B$hueso-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$hueso-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor de huesos o de las articulaciones</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor de huesos o de las articulaciones (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,4</t>
+          <t>0,0; 33,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,87</t>
+          <t>0,0; 57,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,19</t>
+          <t>0,0; 67,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 7,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,47; 34,02</t>
+          <t>4,49; 33,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,97</t>
+          <t>0,0; 24,23</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,15</t>
+          <t>0,0; 28,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 75,33</t>
+          <t>0,0; 75,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,02</t>
+          <t>0,0; 53,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,29</t>
+          <t>0,0; 53,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,86</t>
+          <t>0,0; 30,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,31</t>
+          <t>0,0; 34,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,64</t>
+          <t>0,0; 25,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,89; 38,49</t>
+          <t>4,87; 40,53</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,47</t>
+          <t>0,0; 60,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,98</t>
+          <t>0,0; 38,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,92</t>
+          <t>0,0; 29,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,22</t>
+          <t>0,0; 19,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,49; 34,82</t>
+          <t>4,57; 34,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 7,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 5,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,62</t>
+          <t>0,0; 22,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,38</t>
+          <t>0,0; 19,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 7,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,32; 19,07</t>
+          <t>2,4; 20,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,6</t>
+          <t>0,0; 10,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 3,36</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,65</t>
+          <t>0,0; 36,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,14</t>
+          <t>0,0; 38,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,51</t>
+          <t>0,0; 36,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,21</t>
+          <t>0,0; 58,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,03</t>
+          <t>0,0; 41,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,85</t>
+          <t>0,0; 48,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,71; 36,31</t>
+          <t>4,75; 35,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,09; 31,01</t>
+          <t>3,04; 27,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,87</t>
+          <t>0,0; 27,15</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>0,0; 80,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,7</t>
+          <t>0,0; 80,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,0</t>
+          <t>0,0; 71,34</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,43</t>
+          <t>0,0; 35,65</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,11</t>
+          <t>0,0; 51,91</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,14; 17,5</t>
+          <t>3,15; 16,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,26; 12,79</t>
+          <t>2,29; 14,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,5; 13,84</t>
+          <t>2,72; 15,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,5; 15,09</t>
+          <t>1,78; 15,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,39; 17,09</t>
+          <t>4,44; 17,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,49; 14,68</t>
+          <t>1,62; 13,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,4; 12,06</t>
+          <t>3,91; 12,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,16; 12,46</t>
+          <t>4,12; 12,25</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,22; 11,77</t>
+          <t>3,02; 11,13</t>
         </is>
       </c>
     </row>
@@ -1404,4 +1405,1283 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor de huesos o de las articulaciones (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1464</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2165</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2920</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3828</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2691</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>685; 5106</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3293</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1461</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>832</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>832</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2105</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3460</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3324</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3265</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3010</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2653</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4393</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4533</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>641; 5334</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2658</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3014</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3363</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3030</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1322</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2696</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1322</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>632; 4836</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3423</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4433</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>699; 6063</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4209</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>733</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1551</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1293</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1387</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1304</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2120</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2855</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3036</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4685</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3779</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3489</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3973</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3630</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>677; 5069</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>660; 5955</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4806</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>764</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1556</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2348</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2739</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2772</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3317</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3785</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>3398</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>3727</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>3546</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2904</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>5444</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>2768</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>6302</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>9170</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>6315</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>1306; 6988</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>1389; 8787</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1435; 7968</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>830; 7190</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2606; 10356</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>746; 6323</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>3449; 11226</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>4920; 14617</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>2984; 10989</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$hueso-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$hueso-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor de huesos o de las articulaciones (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor de huesos o de las articulaciones (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -683,7 +683,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,81</t>
+          <t>0,0; 34,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,88</t>
+          <t>0,0; 58,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,49; 33,48</t>
+          <t>4,53; 34,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,23</t>
+          <t>0,0; 21,89</t>
         </is>
       </c>
     </row>
@@ -793,42 +793,42 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,51</t>
+          <t>0,0; 29,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 75,16</t>
+          <t>0,0; 76,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,89</t>
+          <t>0,0; 61,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,89</t>
+          <t>0,0; 53,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,36</t>
+          <t>0,0; 37,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,87</t>
+          <t>0,0; 32,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,58</t>
+          <t>0,0; 23,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,87; 40,53</t>
+          <t>4,87; 37,42</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,93</t>
+          <t>0,0; 60,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,45</t>
+          <t>0,0; 38,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,94</t>
+          <t>0,0; 37,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,69</t>
+          <t>0,0; 19,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,57; 34,97</t>
+          <t>4,6; 37,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,37</t>
+          <t>0,0; 20,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,62</t>
+          <t>0,0; 21,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,4; 20,81</t>
+          <t>2,42; 21,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,53</t>
+          <t>0,0; 11,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,91</t>
+          <t>0,0; 36,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,74</t>
+          <t>0,0; 40,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,79</t>
+          <t>0,0; 36,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,04</t>
+          <t>0,0; 59,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,37</t>
+          <t>0,0; 40,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,84</t>
+          <t>0,0; 40,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,75; 35,61</t>
+          <t>4,76; 37,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,04; 27,45</t>
+          <t>3,05; 29,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,15</t>
+          <t>3,3; 29,91</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,84</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,43</t>
+          <t>0,0; 82,85</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,34</t>
+          <t>0,0; 70,35</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1263,12 +1263,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,65</t>
+          <t>0,0; 35,09</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,91</t>
+          <t>0,0; 59,39</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,15; 16,85</t>
+          <t>3,11; 16,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,29; 14,48</t>
+          <t>2,31; 13,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,72; 15,09</t>
+          <t>2,57; 13,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,78; 15,39</t>
+          <t>1,53; 14,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,44; 17,66</t>
+          <t>4,5; 17,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,62; 13,76</t>
+          <t>1,56; 15,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,91; 12,73</t>
+          <t>3,14; 12,5</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,12; 12,25</t>
+          <t>4,49; 12,92</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,02; 11,13</t>
+          <t>2,85; 11,09</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor de huesos o de las articulaciones (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor de huesos o de las articulaciones (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2920</t>
+          <t>0; 2952</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3828</t>
+          <t>0; 3849</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>685; 5106</t>
+          <t>690; 5197</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3293</t>
+          <t>0; 2974</t>
         </is>
       </c>
     </row>
@@ -1807,42 +1807,42 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3460</t>
+          <t>0; 3567</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3324</t>
+          <t>0; 3371</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3265</t>
+          <t>0; 3740</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3010</t>
+          <t>0; 2997</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2653</t>
+          <t>0; 3246</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4393</t>
+          <t>0; 4041</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4533</t>
+          <t>0; 4165</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>641; 5334</t>
+          <t>641; 4925</t>
         </is>
       </c>
     </row>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2658</t>
+          <t>0; 2651</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3014</t>
+          <t>0; 3009</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3363</t>
+          <t>0; 4157</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3030</t>
+          <t>0; 3072</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>632; 4836</t>
+          <t>637; 5214</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2143,12 +2143,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3423</t>
+          <t>0; 3176</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4433</t>
+          <t>0; 4859</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2158,12 +2158,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>699; 6063</t>
+          <t>705; 6132</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4209</t>
+          <t>0; 4505</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3036</t>
+          <t>0; 2977</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4685</t>
+          <t>0; 4931</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3779</t>
+          <t>0; 3765</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3489</t>
+          <t>0; 3602</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3973</t>
+          <t>0; 3908</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 3630</t>
+          <t>0; 2987</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>677; 5069</t>
+          <t>678; 5296</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>660; 5955</t>
+          <t>661; 6481</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 4806</t>
+          <t>585; 5295</t>
         </is>
       </c>
     </row>
@@ -2459,12 +2459,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 2348</t>
+          <t>0; 2905</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 2739</t>
+          <t>0; 2822</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 2772</t>
+          <t>0; 2734</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3317</t>
+          <t>0; 3264</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 3785</t>
+          <t>0; 4330</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1306; 6988</t>
+          <t>1289; 6803</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1389; 8787</t>
+          <t>1400; 8347</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1435; 7968</t>
+          <t>1358; 7230</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>830; 7190</t>
+          <t>713; 6839</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2606; 10356</t>
+          <t>2636; 10164</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>746; 6323</t>
+          <t>716; 6937</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3449; 11226</t>
+          <t>2771; 11020</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>4920; 14617</t>
+          <t>5353; 15413</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2984; 10989</t>
+          <t>2813; 10953</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$hueso-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$hueso-Clase-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -630,27 +630,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>22,13%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>16,83%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>8,12%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>22,13%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>16,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -683,12 +683,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,18</t>
+          <t>0,0; 66,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 66,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -698,12 +698,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,21</t>
+          <t>0,0; 39,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,53; 34,08</t>
+          <t>4,47; 34,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,89</t>
+          <t>0,0; 25,97</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>13,73%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>13,38%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7,37%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>5,4%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>33,05%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>13,73%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>13,38%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>7,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 53,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,39</t>
+          <t>0,0; 52,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 76,23</t>
+          <t>0,0; 36,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,66</t>
+          <t>0,0; 23,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,14</t>
+          <t>0,0; 75,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,08</t>
+          <t>0,0; 31,31</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,5</t>
+          <t>0,0; 26,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,87; 37,42</t>
+          <t>4,89; 38,49</t>
         </is>
       </c>
     </row>
@@ -845,27 +845,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7,74%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>14,99%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7,74%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -898,12 +898,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 38,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 60,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,01</t>
+          <t>0,0; 29,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,97</t>
+          <t>0,0; 16,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -955,27 +955,27 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4,48%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5,85%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>14,54%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,48%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,85%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,6; 37,71</t>
+          <t>0,0; 23,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 18,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,75</t>
+          <t>4,49; 34,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,42; 21,05</t>
+          <t>2,32; 19,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,27</t>
+          <t>0,0; 10,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>23,07%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>13,58%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9,29%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>8,92%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>12,83%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>12,59%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>23,07%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>13,58%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>9,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,2</t>
+          <t>0,0; 57,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,78</t>
+          <t>0,0; 42,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,66</t>
+          <t>0,0; 38,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,92</t>
+          <t>0,0; 36,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,7</t>
+          <t>0,0; 40,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,2</t>
+          <t>0,0; 40,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,76; 37,2</t>
+          <t>4,71; 36,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,05; 29,87</t>
+          <t>4,09; 31,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,3; 29,91</t>
+          <t>0,0; 26,87</t>
         </is>
       </c>
     </row>
@@ -1180,27 +1180,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>19,66%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>28,17%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>23,25%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>19,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1233,27 +1233,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 71,0</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 82,85</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 70,35</t>
+          <t>0,0; 78,7</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1263,12 +1263,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,09</t>
+          <t>0,0; 39,43</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,39</t>
+          <t>0,0; 51,11</t>
         </is>
       </c>
     </row>
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>6,22%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9,28%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6,03%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>8,19%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>6,14%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>6,72%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>6,22%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9,28%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>6,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,11; 16,4</t>
+          <t>1,5; 15,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,31; 13,76</t>
+          <t>4,39; 17,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,57; 13,69</t>
+          <t>1,49; 14,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,53; 14,64</t>
+          <t>3,14; 17,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,5; 17,33</t>
+          <t>2,26; 12,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,56; 15,1</t>
+          <t>2,5; 13,84</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,14; 12,5</t>
+          <t>3,4; 12,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,49; 12,92</t>
+          <t>4,16; 12,46</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,85; 11,09</t>
+          <t>3,22; 11,77</t>
         </is>
       </c>
     </row>
@@ -1438,14 +1438,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1538,14 +1538,14 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1553,12 +1553,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1591,27 +1591,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>1464</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>701</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1464</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2952</t>
+          <t>0; 4422</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2634</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3849</t>
+          <t>0; 3402</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2691</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>690; 5197</t>
+          <t>682; 5188</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 2974</t>
+          <t>0; 3530</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1706,22 +1706,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1749,32 +1749,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>832</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1461</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>832</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>747</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3212</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3567</t>
+          <t>0; 2920</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3371</t>
+          <t>0; 3221</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3740</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2997</t>
+          <t>0; 2810</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3246</t>
+          <t>0; 3331</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4041</t>
+          <t>0; 3944</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4165</t>
+          <t>0; 4721</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>641; 4925</t>
+          <t>644; 5065</t>
         </is>
       </c>
     </row>
@@ -1859,14 +1859,14 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1912,27 +1912,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>654</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2651</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3056</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2638</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3009</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4157</t>
+          <t>0; 3360</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3072</t>
+          <t>0; 2496</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2022,27 +2022,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -2075,27 +2075,27 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1322</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>2011</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1322</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -2128,12 +2128,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>637; 5214</t>
+          <t>0; 3614</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4155</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2143,12 +2143,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3176</t>
+          <t>621; 4815</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4859</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2158,12 +2158,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>705; 6132</t>
+          <t>676; 5557</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4505</t>
+          <t>0; 4237</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2185,32 +2185,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2238,32 +2238,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1387</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1304</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>733</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1551</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>1293</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1387</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1304</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>690</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 2977</t>
+          <t>0; 3439</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4931</t>
+          <t>0; 4036</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3765</t>
+          <t>0; 2887</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3602</t>
+          <t>0; 3015</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3908</t>
+          <t>0; 4854</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 2987</t>
+          <t>0; 4161</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>678; 5296</t>
+          <t>671; 5169</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>661; 6481</t>
+          <t>887; 6728</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>585; 5295</t>
+          <t>0; 4758</t>
         </is>
       </c>
     </row>
@@ -2353,22 +2353,22 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2406,27 +2406,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>764</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>818</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>792</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>764</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2459,27 +2459,27 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2759</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
           <t>0; 2905</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>0; 2822</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 2734</t>
+          <t>0; 2680</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3264</t>
+          <t>0; 3668</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 4330</t>
+          <t>0; 3727</t>
         </is>
       </c>
     </row>
@@ -2511,32 +2511,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2564,32 +2564,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>2904</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>5444</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2768</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>3398</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>3727</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>3546</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>2904</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>5444</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>2768</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1289; 6803</t>
+          <t>702; 7047</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1400; 8347</t>
+          <t>2571; 10024</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1358; 7230</t>
+          <t>684; 6746</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>713; 6839</t>
+          <t>1304; 7259</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2636; 10164</t>
+          <t>1369; 7764</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>716; 6937</t>
+          <t>1322; 7307</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2771; 11020</t>
+          <t>2994; 10638</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5353; 15413</t>
+          <t>4966; 14873</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2813; 10953</t>
+          <t>3182; 11623</t>
         </is>
       </c>
     </row>
